--- a/推广收集表格 (Responses).xlsx
+++ b/推广收集表格 (Responses).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\我的文件\ACA stuff\Wechat\宣群\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBD7D38-4242-4778-A6D5-AA0D17A5A7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AB4875-A764-431B-AA56-42B9EC68F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="84">
   <si>
     <t>Timestamp</t>
   </si>
@@ -634,6 +634,40 @@
 　　此外，暑假网团也在绝赞进行中！教主再也不用担心我找不到团搭子啦
 　　（主营COC，也有DND及其他规则哟～）</t>
     </r>
+  </si>
+  <si>
+    <t>29/09/2026 17:07:40</t>
+  </si>
+  <si>
+    <t>oliverliu2205@gmail.com</t>
+  </si>
+  <si>
+    <t>我已阅读并同意上述免责与权利保留声明</t>
+  </si>
+  <si>
+    <t>我已阅读并同意上述信息收集及保密条款</t>
+  </si>
+  <si>
+    <t>星星的猹</t>
+  </si>
+  <si>
+    <t>微信群</t>
+  </si>
+  <si>
+    <t>已建立并正在运营 (已有一定群员基础，可直接扫码或加人进群)</t>
+  </si>
+  <si>
+    <t>综合闲聊 / 吹水联络, 唱K，K聚</t>
+  </si>
+  <si>
+    <t>同意入驻，支持 ACA 活动宣传</t>
+  </si>
+  <si>
+    <t>组织jpop、anisongk聚活动，讨论日本流行音乐</t>
+  </si>
+  <si>
+    <t>自我唱功爆上↑↑🎤的同学们注意了⚠️，加入我们hku k聚社摆脱solok无人分担房费的烦恼。我们会不定期举办各种类的jpop、anisong k聚，（如ヨルシカonly、bangdream only等等），也欢迎群友在群里自行组局唱喜欢的歌哦！
+ps:因为k聚绝大多数是日语歌，所以有五十音基础体验会更佳哦</t>
   </si>
 </sst>
 </file>
@@ -643,7 +677,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -678,8 +712,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,12 +737,57 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -707,7 +798,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -719,28 +810,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="适中" xfId="1" builtinId="28"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -765,13 +855,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form responses 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -786,7 +892,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:P9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:P10">
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Email address"/>
@@ -1010,7 +1116,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="18.90625" customWidth="1"/>
@@ -1374,7 +1480,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" s="4" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46222.02691591435</v>
       </c>
@@ -1414,6 +1520,48 @@
       <c r="M9" s="3" t="s">
         <v>67</v>
       </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1765386358</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="8"/>
+      <c r="M10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
